--- a/data/data_raw/eurostat/AT_natural_gas_en_bal_nrg_bal_c.xlsx
+++ b/data/data_raw/eurostat/AT_natural_gas_en_bal_nrg_bal_c.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN140"/>
+  <dimension ref="A1:AO140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,6 +624,11 @@
           <t>2023</t>
         </is>
       </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -748,13 +753,16 @@
         <v>7357.454</v>
       </c>
       <c r="AL2" t="n">
-        <v>6610.231</v>
+        <v>6591.889</v>
       </c>
       <c r="AM2" t="n">
         <v>6211.653</v>
       </c>
       <c r="AN2" t="n">
         <v>5517.902</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>5362.109</v>
       </c>
     </row>
     <row r="3">
@@ -820,6 +828,7 @@
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -947,10 +956,13 @@
         <v>45874.609</v>
       </c>
       <c r="AM4" t="n">
-        <v>119485.8</v>
+        <v>119485.799</v>
       </c>
       <c r="AN4" t="n">
         <v>69644.71400000001</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>52434.124</v>
       </c>
     </row>
     <row r="5">
@@ -1084,6 +1096,9 @@
       <c r="AN5" t="n">
         <v>0</v>
       </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1208,13 +1223,16 @@
         <v>15301.186</v>
       </c>
       <c r="AL6" t="n">
-        <v>37436.68</v>
+        <v>37455.019</v>
       </c>
       <c r="AM6" t="n">
-        <v>-45569.599</v>
+        <v>-45569.6</v>
       </c>
       <c r="AN6" t="n">
         <v>-6628.859</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>10074.195</v>
       </c>
     </row>
     <row r="7">
@@ -1340,13 +1358,16 @@
         <v>85118.71400000001</v>
       </c>
       <c r="AL7" t="n">
-        <v>89921.52</v>
+        <v>89921.51700000001</v>
       </c>
       <c r="AM7" t="n">
-        <v>80127.853</v>
+        <v>80127.852</v>
       </c>
       <c r="AN7" t="n">
         <v>68533.757</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>67870.428</v>
       </c>
     </row>
     <row r="8">
@@ -1480,6 +1501,9 @@
       <c r="AN8" t="n">
         <v>0</v>
       </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1604,13 +1628,16 @@
         <v>85118.71400000001</v>
       </c>
       <c r="AL9" t="n">
-        <v>89921.52</v>
+        <v>89921.51700000001</v>
       </c>
       <c r="AM9" t="n">
-        <v>80127.853</v>
+        <v>80127.852</v>
       </c>
       <c r="AN9" t="n">
         <v>68533.757</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>67870.428</v>
       </c>
     </row>
     <row r="10">
@@ -1676,6 +1703,7 @@
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1800,13 +1828,16 @@
         <v>85118.71400000001</v>
       </c>
       <c r="AL11" t="n">
-        <v>89921.52</v>
+        <v>89921.51700000001</v>
       </c>
       <c r="AM11" t="n">
-        <v>80127.853</v>
+        <v>80127.852</v>
       </c>
       <c r="AN11" t="n">
         <v>68533.757</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>67870.428</v>
       </c>
     </row>
     <row r="12">
@@ -1872,6 +1903,7 @@
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1936,6 +1968,7 @@
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -2000,6 +2033,7 @@
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -2127,10 +2161,13 @@
         <v>25859.042</v>
       </c>
       <c r="AM15" t="n">
-        <v>23860.408</v>
+        <v>23860.876</v>
       </c>
       <c r="AN15" t="n">
-        <v>17964.506</v>
+        <v>17972.352</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>18481.455</v>
       </c>
     </row>
     <row r="16">
@@ -2259,10 +2296,13 @@
         <v>25859.042</v>
       </c>
       <c r="AM16" t="n">
-        <v>23860.408</v>
+        <v>23860.876</v>
       </c>
       <c r="AN16" t="n">
-        <v>17964.506</v>
+        <v>17972.352</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>18481.455</v>
       </c>
     </row>
     <row r="17">
@@ -2388,13 +2428,16 @@
         <v>6144.256</v>
       </c>
       <c r="AL17" t="n">
-        <v>4098.508</v>
+        <v>4098.509</v>
       </c>
       <c r="AM17" t="n">
         <v>6821.18</v>
       </c>
       <c r="AN17" t="n">
         <v>3508.415</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>3539.234</v>
       </c>
     </row>
     <row r="18">
@@ -2528,6 +2571,9 @@
       <c r="AN18" t="n">
         <v>10734.574</v>
       </c>
+      <c r="AO18" t="n">
+        <v>10846.734</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -2655,10 +2701,13 @@
         <v>2291.732</v>
       </c>
       <c r="AM19" t="n">
-        <v>1558.18</v>
+        <v>1558.648</v>
       </c>
       <c r="AN19" t="n">
-        <v>1717.552</v>
+        <v>1725.037</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1964.671</v>
       </c>
     </row>
     <row r="20">
@@ -2792,6 +2841,9 @@
       <c r="AN20" t="n">
         <v>383.096</v>
       </c>
+      <c r="AO20" t="n">
+        <v>395.63</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -2924,6 +2976,9 @@
       <c r="AN21" t="n">
         <v>1605.56</v>
       </c>
+      <c r="AO21" t="n">
+        <v>1721.43</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -3045,7 +3100,7 @@
         <v>35.025</v>
       </c>
       <c r="AK22" t="n">
-        <v>15.468</v>
+        <v>15.467</v>
       </c>
       <c r="AL22" t="n">
         <v>19.329</v>
@@ -3054,7 +3109,10 @@
         <v>13.689</v>
       </c>
       <c r="AN22" t="n">
-        <v>15.309</v>
+        <v>15.669</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>13.756</v>
       </c>
     </row>
     <row r="23">
@@ -3120,6 +3178,7 @@
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -3184,6 +3243,7 @@
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -3248,6 +3308,7 @@
       <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -3312,6 +3373,7 @@
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -3376,6 +3438,7 @@
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -3508,6 +3571,9 @@
       <c r="AN28" t="n">
         <v>0</v>
       </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -3640,6 +3706,9 @@
       <c r="AN29" t="n">
         <v>0</v>
       </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -3770,6 +3839,9 @@
         <v>0</v>
       </c>
       <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3836,6 +3908,7 @@
       <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -3900,6 +3973,7 @@
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="inlineStr"/>
       <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -3964,6 +4038,7 @@
       <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="inlineStr"/>
       <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -4028,6 +4103,7 @@
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -4092,6 +4168,7 @@
       <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="inlineStr"/>
       <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -4156,6 +4233,7 @@
       <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="inlineStr"/>
       <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -4220,6 +4298,7 @@
       <c r="AL37" t="inlineStr"/>
       <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -4284,6 +4363,7 @@
       <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -4348,6 +4428,7 @@
       <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -4412,6 +4493,7 @@
       <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -4476,6 +4558,7 @@
       <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -4540,6 +4623,7 @@
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -4604,6 +4688,7 @@
       <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -4736,6 +4821,9 @@
       <c r="AN44" t="n">
         <v>0</v>
       </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -4868,6 +4956,9 @@
       <c r="AN45" t="n">
         <v>0</v>
       </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -4999,6 +5090,9 @@
       </c>
       <c r="AN46" t="n">
         <v>120.635</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>111.172</v>
       </c>
     </row>
     <row r="47">
@@ -5064,6 +5158,7 @@
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr"/>
       <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -5128,6 +5223,7 @@
       <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="inlineStr"/>
       <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -5192,6 +5288,7 @@
       <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="inlineStr"/>
       <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -5256,6 +5353,7 @@
       <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="inlineStr"/>
       <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -5320,6 +5418,7 @@
       <c r="AL51" t="inlineStr"/>
       <c r="AM51" t="inlineStr"/>
       <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -5384,6 +5483,7 @@
       <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="inlineStr"/>
       <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -5448,6 +5548,7 @@
       <c r="AL53" t="inlineStr"/>
       <c r="AM53" t="inlineStr"/>
       <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -5512,6 +5613,7 @@
       <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="inlineStr"/>
       <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -5576,6 +5678,7 @@
       <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="inlineStr"/>
       <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -5640,6 +5743,7 @@
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="inlineStr"/>
       <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -5704,6 +5808,7 @@
       <c r="AL57" t="inlineStr"/>
       <c r="AM57" t="inlineStr"/>
       <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -5768,6 +5873,7 @@
       <c r="AL58" t="inlineStr"/>
       <c r="AM58" t="inlineStr"/>
       <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -5832,6 +5938,7 @@
       <c r="AL59" t="inlineStr"/>
       <c r="AM59" t="inlineStr"/>
       <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -5896,6 +6003,7 @@
       <c r="AL60" t="inlineStr"/>
       <c r="AM60" t="inlineStr"/>
       <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -5960,6 +6068,7 @@
       <c r="AL61" t="inlineStr"/>
       <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -6024,6 +6133,7 @@
       <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="inlineStr"/>
       <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -6088,6 +6198,7 @@
       <c r="AL63" t="inlineStr"/>
       <c r="AM63" t="inlineStr"/>
       <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -6152,6 +6263,7 @@
       <c r="AL64" t="inlineStr"/>
       <c r="AM64" t="inlineStr"/>
       <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -6216,6 +6328,7 @@
       <c r="AL65" t="inlineStr"/>
       <c r="AM65" t="inlineStr"/>
       <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -6280,6 +6393,7 @@
       <c r="AL66" t="inlineStr"/>
       <c r="AM66" t="inlineStr"/>
       <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -6344,6 +6458,7 @@
       <c r="AL67" t="inlineStr"/>
       <c r="AM67" t="inlineStr"/>
       <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -6408,6 +6523,7 @@
       <c r="AL68" t="inlineStr"/>
       <c r="AM68" t="inlineStr"/>
       <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -6472,6 +6588,7 @@
       <c r="AL69" t="inlineStr"/>
       <c r="AM69" t="inlineStr"/>
       <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -6536,6 +6653,7 @@
       <c r="AL70" t="inlineStr"/>
       <c r="AM70" t="inlineStr"/>
       <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -6667,6 +6785,9 @@
       </c>
       <c r="AN71" t="n">
         <v>120.635</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>111.172</v>
       </c>
     </row>
     <row r="72">
@@ -6732,6 +6853,7 @@
       <c r="AL72" t="inlineStr"/>
       <c r="AM72" t="inlineStr"/>
       <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -6796,6 +6918,7 @@
       <c r="AL73" t="inlineStr"/>
       <c r="AM73" t="inlineStr"/>
       <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -6860,6 +6983,7 @@
       <c r="AL74" t="inlineStr"/>
       <c r="AM74" t="inlineStr"/>
       <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -6924,6 +7048,7 @@
       <c r="AL75" t="inlineStr"/>
       <c r="AM75" t="inlineStr"/>
       <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -7045,16 +7170,19 @@
         <v>2905.443</v>
       </c>
       <c r="AK76" t="n">
-        <v>2491.261</v>
+        <v>2491.26</v>
       </c>
       <c r="AL76" t="n">
         <v>2834.065</v>
       </c>
       <c r="AM76" t="n">
-        <v>2195.194</v>
+        <v>2195.193</v>
       </c>
       <c r="AN76" t="n">
         <v>2140.541</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>2557.911</v>
       </c>
     </row>
     <row r="77">
@@ -7188,6 +7316,9 @@
       <c r="AN77" t="n">
         <v>0</v>
       </c>
+      <c r="AO77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -7320,6 +7451,9 @@
       <c r="AN78" t="n">
         <v>0</v>
       </c>
+      <c r="AO78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -7441,7 +7575,7 @@
         <v>803.789</v>
       </c>
       <c r="AK79" t="n">
-        <v>762.13</v>
+        <v>762.129</v>
       </c>
       <c r="AL79" t="n">
         <v>893.098</v>
@@ -7451,6 +7585,9 @@
       </c>
       <c r="AN79" t="n">
         <v>677.857</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>793.939</v>
       </c>
     </row>
     <row r="80">
@@ -7516,6 +7653,7 @@
       <c r="AL80" t="inlineStr"/>
       <c r="AM80" t="inlineStr"/>
       <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -7647,6 +7785,9 @@
       </c>
       <c r="AN81" t="n">
         <v>58.265</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>46.731</v>
       </c>
     </row>
     <row r="82">
@@ -7712,6 +7853,7 @@
       <c r="AL82" t="inlineStr"/>
       <c r="AM82" t="inlineStr"/>
       <c r="AN82" t="inlineStr"/>
+      <c r="AO82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -7844,6 +7986,9 @@
       <c r="AN83" t="n">
         <v>0</v>
       </c>
+      <c r="AO83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -7976,6 +8121,9 @@
       <c r="AN84" t="n">
         <v>455.313</v>
       </c>
+      <c r="AO84" t="n">
+        <v>434.959</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -8100,13 +8248,16 @@
         <v>1329.4</v>
       </c>
       <c r="AL85" t="n">
-        <v>1449.092</v>
+        <v>1449.093</v>
       </c>
       <c r="AM85" t="n">
         <v>834.571</v>
       </c>
       <c r="AN85" t="n">
         <v>949.106</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>1282.282</v>
       </c>
     </row>
     <row r="86">
@@ -8172,6 +8323,7 @@
       <c r="AL86" t="inlineStr"/>
       <c r="AM86" t="inlineStr"/>
       <c r="AN86" t="inlineStr"/>
+      <c r="AO86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -8236,6 +8388,7 @@
       <c r="AL87" t="inlineStr"/>
       <c r="AM87" t="inlineStr"/>
       <c r="AN87" t="inlineStr"/>
+      <c r="AO87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -8366,6 +8519,9 @@
         <v>0</v>
       </c>
       <c r="AN88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8432,6 +8588,7 @@
       <c r="AL89" t="inlineStr"/>
       <c r="AM89" t="inlineStr"/>
       <c r="AN89" t="inlineStr"/>
+      <c r="AO89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -8562,6 +8719,9 @@
         <v>0</v>
       </c>
       <c r="AN90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8628,6 +8788,7 @@
       <c r="AL91" t="inlineStr"/>
       <c r="AM91" t="inlineStr"/>
       <c r="AN91" t="inlineStr"/>
+      <c r="AO91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -8760,6 +8921,9 @@
       <c r="AN92" t="n">
         <v>0</v>
       </c>
+      <c r="AO92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -8881,16 +9045,19 @@
         <v>30.841</v>
       </c>
       <c r="AK93" t="n">
-        <v>31.164</v>
+        <v>31.163</v>
       </c>
       <c r="AL93" t="n">
         <v>24.858</v>
       </c>
       <c r="AM93" t="n">
-        <v>18.828</v>
+        <v>60.572</v>
       </c>
       <c r="AN93" t="n">
-        <v>9.375999999999999</v>
+        <v>41.594</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>35.508</v>
       </c>
     </row>
     <row r="94">
@@ -9013,16 +9180,19 @@
         <v>59744.405</v>
       </c>
       <c r="AK94" t="n">
-        <v>58454.584</v>
+        <v>58454.585</v>
       </c>
       <c r="AL94" t="n">
-        <v>61326.068</v>
+        <v>61326.065</v>
       </c>
       <c r="AM94" t="n">
-        <v>54176.552</v>
+        <v>54134.339</v>
       </c>
       <c r="AN94" t="n">
-        <v>48539.969</v>
+        <v>48499.905</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>46906.727</v>
       </c>
     </row>
     <row r="95">
@@ -9145,16 +9315,19 @@
         <v>4129.559</v>
       </c>
       <c r="AK95" t="n">
-        <v>3938.031</v>
+        <v>3938.032</v>
       </c>
       <c r="AL95" t="n">
-        <v>3829.838</v>
+        <v>3829.841</v>
       </c>
       <c r="AM95" t="n">
-        <v>3413.176</v>
+        <v>3413.172</v>
       </c>
       <c r="AN95" t="n">
-        <v>3558.583</v>
+        <v>3558.578</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>3064.174</v>
       </c>
     </row>
     <row r="96">
@@ -9277,16 +9450,19 @@
         <v>4129.559</v>
       </c>
       <c r="AK96" t="n">
-        <v>3938.031</v>
+        <v>3938.032</v>
       </c>
       <c r="AL96" t="n">
-        <v>3829.838</v>
+        <v>3829.841</v>
       </c>
       <c r="AM96" t="n">
-        <v>3413.176</v>
+        <v>3413.172</v>
       </c>
       <c r="AN96" t="n">
-        <v>3558.583</v>
+        <v>3558.578</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>3064.174</v>
       </c>
     </row>
     <row r="97">
@@ -9352,6 +9528,7 @@
       <c r="AL97" t="inlineStr"/>
       <c r="AM97" t="inlineStr"/>
       <c r="AN97" t="inlineStr"/>
+      <c r="AO97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -9416,6 +9593,7 @@
       <c r="AL98" t="inlineStr"/>
       <c r="AM98" t="inlineStr"/>
       <c r="AN98" t="inlineStr"/>
+      <c r="AO98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -9537,16 +9715,19 @@
         <v>4129.559</v>
       </c>
       <c r="AK99" t="n">
-        <v>3938.031</v>
+        <v>3938.032</v>
       </c>
       <c r="AL99" t="n">
-        <v>3829.838</v>
+        <v>3829.841</v>
       </c>
       <c r="AM99" t="n">
-        <v>3413.176</v>
+        <v>3413.172</v>
       </c>
       <c r="AN99" t="n">
-        <v>3558.583</v>
+        <v>3558.578</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>3064.174</v>
       </c>
     </row>
     <row r="100">
@@ -9680,6 +9861,9 @@
       <c r="AN100" t="n">
         <v>0</v>
       </c>
+      <c r="AO100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -9812,6 +9996,9 @@
       <c r="AN101" t="n">
         <v>0</v>
       </c>
+      <c r="AO101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -9933,16 +10120,19 @@
         <v>55614.85</v>
       </c>
       <c r="AK102" t="n">
-        <v>54516.555</v>
+        <v>54516.552</v>
       </c>
       <c r="AL102" t="n">
-        <v>57496.228</v>
+        <v>57496.226</v>
       </c>
       <c r="AM102" t="n">
-        <v>50763.375</v>
+        <v>50721.168</v>
       </c>
       <c r="AN102" t="n">
-        <v>44981.385</v>
+        <v>44941.327</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>43842.553</v>
       </c>
     </row>
     <row r="103">
@@ -10065,16 +10255,19 @@
         <v>31579.639</v>
       </c>
       <c r="AK103" t="n">
-        <v>30895.091</v>
+        <v>30895.111</v>
       </c>
       <c r="AL103" t="n">
-        <v>32387.495</v>
+        <v>32489.449</v>
       </c>
       <c r="AM103" t="n">
-        <v>30909.221</v>
+        <v>30880.745</v>
       </c>
       <c r="AN103" t="n">
-        <v>26870.511</v>
+        <v>26843.514</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>26416.988</v>
       </c>
     </row>
     <row r="104">
@@ -10197,16 +10390,19 @@
         <v>4893.758</v>
       </c>
       <c r="AK104" t="n">
-        <v>4772.169</v>
+        <v>4772.173</v>
       </c>
       <c r="AL104" t="n">
-        <v>4400.201</v>
+        <v>4415.36</v>
       </c>
       <c r="AM104" t="n">
-        <v>4795.352</v>
+        <v>4790.46</v>
       </c>
       <c r="AN104" t="n">
-        <v>4722.458</v>
+        <v>4717.2</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>4516.634</v>
       </c>
     </row>
     <row r="105">
@@ -10329,16 +10525,19 @@
         <v>5437.382</v>
       </c>
       <c r="AK105" t="n">
-        <v>5223.125</v>
+        <v>5223.127</v>
       </c>
       <c r="AL105" t="n">
-        <v>5762.561</v>
+        <v>5780.718</v>
       </c>
       <c r="AM105" t="n">
-        <v>4750.481</v>
+        <v>4746.097</v>
       </c>
       <c r="AN105" t="n">
-        <v>4422.369</v>
+        <v>4417.842</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>4807.307</v>
       </c>
     </row>
     <row r="106">
@@ -10461,16 +10660,19 @@
         <v>1391.993</v>
       </c>
       <c r="AK106" t="n">
-        <v>1229.23</v>
+        <v>1229.239</v>
       </c>
       <c r="AL106" t="n">
-        <v>1398.372</v>
+        <v>1402.398</v>
       </c>
       <c r="AM106" t="n">
-        <v>1437.924</v>
+        <v>1436.732</v>
       </c>
       <c r="AN106" t="n">
-        <v>1303.275</v>
+        <v>1302.076</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>1255.513</v>
       </c>
     </row>
     <row r="107">
@@ -10596,13 +10798,16 @@
         <v>4556.233</v>
       </c>
       <c r="AL107" t="n">
-        <v>5256.973</v>
+        <v>5274.611</v>
       </c>
       <c r="AM107" t="n">
-        <v>4678.588</v>
+        <v>4673.962</v>
       </c>
       <c r="AN107" t="n">
-        <v>3850.536</v>
+        <v>3846.383</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>3883.368</v>
       </c>
     </row>
     <row r="108">
@@ -10728,13 +10933,16 @@
         <v>470.175</v>
       </c>
       <c r="AL108" t="n">
-        <v>509.762</v>
+        <v>511.418</v>
       </c>
       <c r="AM108" t="n">
-        <v>558.013</v>
+        <v>557.471</v>
       </c>
       <c r="AN108" t="n">
-        <v>310.447</v>
+        <v>310.124</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>213.86</v>
       </c>
     </row>
     <row r="109">
@@ -10860,13 +11068,16 @@
         <v>1669.081</v>
       </c>
       <c r="AL109" t="n">
-        <v>1852.069</v>
+        <v>1857.414</v>
       </c>
       <c r="AM109" t="n">
-        <v>1785.982</v>
+        <v>1784.507</v>
       </c>
       <c r="AN109" t="n">
-        <v>1566.127</v>
+        <v>1564.729</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>1451.963</v>
       </c>
     </row>
     <row r="110">
@@ -10992,13 +11203,16 @@
         <v>1630.851</v>
       </c>
       <c r="AL110" t="n">
-        <v>1148.691</v>
+        <v>1152.417</v>
       </c>
       <c r="AM110" t="n">
-        <v>1099.761</v>
+        <v>1098.632</v>
       </c>
       <c r="AN110" t="n">
-        <v>671.404</v>
+        <v>670.651</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>679.224</v>
       </c>
     </row>
     <row r="111">
@@ -11121,16 +11335,19 @@
         <v>3357.337</v>
       </c>
       <c r="AK111" t="n">
-        <v>3567.944</v>
+        <v>3567.946</v>
       </c>
       <c r="AL111" t="n">
-        <v>3666.355</v>
+        <v>3676.535</v>
       </c>
       <c r="AM111" t="n">
-        <v>3900.966</v>
+        <v>3897.744</v>
       </c>
       <c r="AN111" t="n">
-        <v>3095.959</v>
+        <v>3093.271</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>3805.311</v>
       </c>
     </row>
     <row r="112">
@@ -11253,16 +11470,19 @@
         <v>6624.318</v>
       </c>
       <c r="AK112" t="n">
-        <v>6051.146</v>
+        <v>6051.147</v>
       </c>
       <c r="AL112" t="n">
-        <v>6427.933</v>
+        <v>6449.308</v>
       </c>
       <c r="AM112" t="n">
-        <v>5768.811</v>
+        <v>5763.306</v>
       </c>
       <c r="AN112" t="n">
-        <v>4698.533</v>
+        <v>4693.583</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>3970.454</v>
       </c>
     </row>
     <row r="113">
@@ -11388,13 +11608,16 @@
         <v>573.21</v>
       </c>
       <c r="AL113" t="n">
-        <v>705.581</v>
+        <v>707.46</v>
       </c>
       <c r="AM113" t="n">
-        <v>672.909</v>
+        <v>672.39</v>
       </c>
       <c r="AN113" t="n">
-        <v>828.729</v>
+        <v>827.967</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>632.7910000000001</v>
       </c>
     </row>
     <row r="114">
@@ -11520,13 +11743,16 @@
         <v>337.932</v>
       </c>
       <c r="AL114" t="n">
-        <v>317.586</v>
+        <v>318.338</v>
       </c>
       <c r="AM114" t="n">
-        <v>557.889</v>
+        <v>557.487</v>
       </c>
       <c r="AN114" t="n">
-        <v>542.971</v>
+        <v>542.581</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>453.102</v>
       </c>
     </row>
     <row r="115">
@@ -11652,13 +11878,16 @@
         <v>386.585</v>
       </c>
       <c r="AL115" t="n">
-        <v>434.73</v>
+        <v>435.504</v>
       </c>
       <c r="AM115" t="n">
-        <v>385.159</v>
+        <v>384.951</v>
       </c>
       <c r="AN115" t="n">
-        <v>375.791</v>
+        <v>375.585</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>322.849</v>
       </c>
     </row>
     <row r="116">
@@ -11784,13 +12013,16 @@
         <v>427.411</v>
       </c>
       <c r="AL116" t="n">
-        <v>506.68</v>
+        <v>507.969</v>
       </c>
       <c r="AM116" t="n">
-        <v>517.3869999999999</v>
+        <v>517.008</v>
       </c>
       <c r="AN116" t="n">
-        <v>481.911</v>
+        <v>481.519</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>424.615</v>
       </c>
     </row>
     <row r="117">
@@ -11913,16 +12145,19 @@
         <v>2920.01</v>
       </c>
       <c r="AK117" t="n">
-        <v>2583.737</v>
+        <v>2583.736</v>
       </c>
       <c r="AL117" t="n">
         <v>2085.082</v>
       </c>
       <c r="AM117" t="n">
-        <v>965.104</v>
+        <v>962.415</v>
       </c>
       <c r="AN117" t="n">
-        <v>303.812</v>
+        <v>301.147</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>288.371</v>
       </c>
     </row>
     <row r="118">
@@ -11988,6 +12223,7 @@
       <c r="AL118" t="inlineStr"/>
       <c r="AM118" t="inlineStr"/>
       <c r="AN118" t="inlineStr"/>
+      <c r="AO118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -12115,10 +12351,13 @@
         <v>215.744</v>
       </c>
       <c r="AM119" t="n">
-        <v>207.383</v>
+        <v>204.695</v>
       </c>
       <c r="AN119" t="n">
-        <v>189.129</v>
+        <v>186.464</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>171.604</v>
       </c>
     </row>
     <row r="120">
@@ -12184,6 +12423,7 @@
       <c r="AL120" t="inlineStr"/>
       <c r="AM120" t="inlineStr"/>
       <c r="AN120" t="inlineStr"/>
+      <c r="AO120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -12248,6 +12488,7 @@
       <c r="AL121" t="inlineStr"/>
       <c r="AM121" t="inlineStr"/>
       <c r="AN121" t="inlineStr"/>
+      <c r="AO121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -12369,7 +12610,7 @@
         <v>2706.665</v>
       </c>
       <c r="AK122" t="n">
-        <v>2357.481</v>
+        <v>2357.48</v>
       </c>
       <c r="AL122" t="n">
         <v>1869.338</v>
@@ -12379,6 +12620,9 @@
       </c>
       <c r="AN122" t="n">
         <v>114.683</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>116.767</v>
       </c>
     </row>
     <row r="123">
@@ -12512,6 +12756,9 @@
       <c r="AN123" t="n">
         <v>0</v>
       </c>
+      <c r="AO123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -12633,16 +12880,19 @@
         <v>21115.201</v>
       </c>
       <c r="AK124" t="n">
-        <v>21037.727</v>
+        <v>21037.704</v>
       </c>
       <c r="AL124" t="n">
-        <v>23023.651</v>
+        <v>22921.694</v>
       </c>
       <c r="AM124" t="n">
-        <v>18889.051</v>
+        <v>18878.008</v>
       </c>
       <c r="AN124" t="n">
-        <v>17807.061</v>
+        <v>17796.667</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>17137.194</v>
       </c>
     </row>
     <row r="125">
@@ -12765,16 +13015,19 @@
         <v>4222.214</v>
       </c>
       <c r="AK125" t="n">
-        <v>4045.823</v>
+        <v>4045.811</v>
       </c>
       <c r="AL125" t="n">
-        <v>4619.382</v>
+        <v>4480.403</v>
       </c>
       <c r="AM125" t="n">
-        <v>3536.89</v>
+        <v>3534.968</v>
       </c>
       <c r="AN125" t="n">
-        <v>3942.222</v>
+        <v>3940.824</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>4330.656</v>
       </c>
     </row>
     <row r="126">
@@ -12897,16 +13150,19 @@
         <v>16588.704</v>
       </c>
       <c r="AK126" t="n">
-        <v>16738.764</v>
+        <v>16738.77</v>
       </c>
       <c r="AL126" t="n">
-        <v>18132.41</v>
+        <v>18169.438</v>
       </c>
       <c r="AM126" t="n">
-        <v>15116.33</v>
+        <v>15107.36</v>
       </c>
       <c r="AN126" t="n">
-        <v>13734.515</v>
+        <v>13725.567</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>12663.236</v>
       </c>
     </row>
     <row r="127">
@@ -13029,16 +13285,19 @@
         <v>304.283</v>
       </c>
       <c r="AK127" t="n">
-        <v>253.14</v>
+        <v>252.529</v>
       </c>
       <c r="AL127" t="n">
-        <v>271.858</v>
+        <v>271.059</v>
       </c>
       <c r="AM127" t="n">
-        <v>235.83</v>
+        <v>234.97</v>
       </c>
       <c r="AN127" t="n">
-        <v>130.325</v>
+        <v>129.87</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>142.855</v>
       </c>
     </row>
     <row r="128">
@@ -13161,16 +13420,19 @@
         <v>0</v>
       </c>
       <c r="AK128" t="n">
-        <v>0</v>
+        <v>0.594</v>
       </c>
       <c r="AL128" t="n">
-        <v>0</v>
+        <v>0.794</v>
       </c>
       <c r="AM128" t="n">
-        <v>0</v>
+        <v>0.711</v>
       </c>
       <c r="AN128" t="n">
-        <v>0</v>
+        <v>0.406</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.447</v>
       </c>
     </row>
     <row r="129">
@@ -13304,6 +13566,9 @@
       <c r="AN129" t="n">
         <v>0</v>
       </c>
+      <c r="AO129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -13425,16 +13690,19 @@
         <v>-0.004</v>
       </c>
       <c r="AK130" t="n">
-        <v>-0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AL130" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="AM130" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AN130" t="n">
-        <v>0.001</v>
+        <v>0</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -13563,10 +13831,13 @@
         <v>10617.882</v>
       </c>
       <c r="AM131" t="n">
-        <v>10873.57</v>
+        <v>10853.246</v>
       </c>
       <c r="AN131" t="n">
-        <v>7495.264</v>
+        <v>7495.265</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>7536.924</v>
       </c>
     </row>
     <row r="132">
@@ -13695,10 +13966,13 @@
         <v>2330.167</v>
       </c>
       <c r="AM132" t="n">
-        <v>4352.37</v>
+        <v>4329.018</v>
       </c>
       <c r="AN132" t="n">
-        <v>2138.721</v>
+        <v>2141.547</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>2068.624</v>
       </c>
     </row>
     <row r="133">
@@ -13827,10 +14101,13 @@
         <v>6500.899</v>
       </c>
       <c r="AM133" t="n">
-        <v>5145.305</v>
+        <v>5148.333</v>
       </c>
       <c r="AN133" t="n">
-        <v>4165.012</v>
+        <v>4162.187</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>4259.897</v>
       </c>
     </row>
     <row r="134">
@@ -13964,6 +14241,9 @@
       <c r="AN134" t="n">
         <v>200.886</v>
       </c>
+      <c r="AO134" t="n">
+        <v>202.851</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -14096,6 +14376,9 @@
       <c r="AN135" t="n">
         <v>990.645</v>
       </c>
+      <c r="AO135" t="n">
+        <v>1005.552</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -14223,10 +14506,13 @@
         <v>9104.852000000001</v>
       </c>
       <c r="AM136" t="n">
-        <v>7409.135</v>
+        <v>7409.504</v>
       </c>
       <c r="AN136" t="n">
-        <v>6574.057</v>
+        <v>6581.12</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>6924.539</v>
       </c>
     </row>
     <row r="137">
@@ -14360,6 +14646,9 @@
       <c r="AN137" t="n">
         <v>4710.791</v>
       </c>
+      <c r="AO137" t="n">
+        <v>4824.082</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -14487,10 +14776,13 @@
         <v>2047.973</v>
       </c>
       <c r="AM138" t="n">
-        <v>1338.574</v>
+        <v>1338.943</v>
       </c>
       <c r="AN138" t="n">
-        <v>1541.025</v>
+        <v>1547.764</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1782.147</v>
       </c>
     </row>
     <row r="139">
@@ -14624,6 +14916,9 @@
       <c r="AN139" t="n">
         <v>308.438</v>
       </c>
+      <c r="AO139" t="n">
+        <v>305.908</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -14754,7 +15049,10 @@
         <v>12.32</v>
       </c>
       <c r="AN140" t="n">
-        <v>13.803</v>
+        <v>14.127</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>12.402</v>
       </c>
     </row>
   </sheetData>
